--- a/src/test/resources/TestData/UserInfo.xlsx
+++ b/src/test/resources/TestData/UserInfo.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="UserCredintials" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -460,4 +461,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/TestData/UserInfo.xlsx
+++ b/src/test/resources/TestData/UserInfo.xlsx
@@ -13,7 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="UserCredintials" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="newCreatedSheet" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>UserName</t>
   </si>
@@ -55,6 +55,21 @@
   </si>
   <si>
     <t>Pass@4567</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>bruce@gmail.com</t>
+  </si>
+  <si>
+    <t>Password@0987</t>
+  </si>
+  <si>
+    <t>NewCell_1</t>
+  </si>
+  <si>
+    <t>NewCell_2</t>
   </si>
 </sst>
 </file>
@@ -400,22 +415,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -423,7 +441,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -431,7 +449,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -439,12 +457,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -465,9 +491,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>